--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -1110,7 +1110,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>源题号</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>P3083</t>
+  </si>
+  <si>
+    <t>P16953</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1014,8 +1017,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1039,6 +1042,14 @@
       </c>
       <c r="B3">
         <v>594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -1063,7 +1074,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1091,7 +1102,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1099,7 +1110,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1107,7 +1118,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>593</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>源题号</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>P16953</t>
+  </si>
+  <si>
+    <t>P1469</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1017,8 +1020,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1050,6 +1053,14 @@
       </c>
       <c r="B4">
         <v>595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1085,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1102,7 +1113,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1110,7 +1121,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1118,7 +1129,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>593</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -1060,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>220</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>源题号</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>P1469</t>
+  </si>
+  <si>
+    <t>B4261</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1020,8 +1023,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1061,6 +1064,14 @@
       </c>
       <c r="B5">
         <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1085,7 +1096,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1113,7 +1124,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1121,7 +1132,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1129,7 +1140,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>593</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>源题号</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>B4261</t>
+  </si>
+  <si>
+    <t>P1079</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1023,8 +1026,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1072,6 +1075,14 @@
       </c>
       <c r="B6">
         <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -1084,7 +1095,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1096,7 +1107,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1112,7 +1123,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1124,7 +1135,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1132,7 +1143,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1140,7 +1151,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>593</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>源题号</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>abc280d</t>
+  </si>
+  <si>
+    <t>abc171e</t>
   </si>
 </sst>
 </file>
@@ -1027,7 +1030,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1095,7 +1098,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1122,8 +1125,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1155,6 +1158,14 @@
       </c>
       <c r="B4">
         <v>593</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="2"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>源题号</t>
   </si>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>P1079</t>
+  </si>
+  <si>
+    <t>U704880</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1029,8 +1032,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1086,6 +1089,14 @@
       </c>
       <c r="B7">
         <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8">
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1110,7 +1121,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1126,7 +1137,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1138,7 +1149,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1146,7 +1157,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1154,7 +1165,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1162,7 +1173,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>源题号</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>U704880</t>
+  </si>
+  <si>
+    <t>U705176</t>
+  </si>
+  <si>
+    <t>U704901</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1032,8 +1038,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1097,6 +1103,22 @@
       </c>
       <c r="B8">
         <v>601</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>602</v>
       </c>
     </row>
   </sheetData>
@@ -1121,7 +1143,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1149,7 +1171,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1157,7 +1179,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1165,7 +1187,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1173,7 +1195,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowHeight="17800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>源题号</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>cf1668b</t>
+  </si>
+  <si>
+    <t>cf1999e</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1130,8 +1133,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1147,6 +1150,14 @@
       </c>
       <c r="B2">
         <v>592</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -1171,7 +1182,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1179,7 +1190,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1187,7 +1198,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1195,7 +1206,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>源题号</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>U704901</t>
+  </si>
+  <si>
+    <t>U705882</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1041,8 +1044,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1122,6 +1125,14 @@
       </c>
       <c r="B10">
         <v>602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>605</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1145,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1146,7 +1157,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1154,7 +1165,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1170,7 +1181,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1182,7 +1193,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1190,7 +1201,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1198,7 +1209,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1206,7 +1217,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>源题号</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>U705882</t>
+  </si>
+  <si>
+    <t>P1944</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1044,8 +1047,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1133,6 +1136,14 @@
       </c>
       <c r="B11">
         <v>605</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>606</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1156,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1157,7 +1168,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1165,7 +1176,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1181,7 +1192,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1193,7 +1204,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1201,7 +1212,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1209,7 +1220,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1217,7 +1228,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowHeight="17800" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>源题号</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>cf1999e</t>
+  </si>
+  <si>
+    <t>cf26b</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1155,8 +1158,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1180,6 +1183,14 @@
       </c>
       <c r="B3">
         <v>604</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1215,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1212,7 +1223,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1220,7 +1231,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1228,7 +1239,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>源题号</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>P1944</t>
+  </si>
+  <si>
+    <t>P14361</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1050,8 +1053,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1147,6 +1150,14 @@
       </c>
       <c r="B12">
         <v>606</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -1159,7 +1170,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1171,7 +1182,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1179,7 +1190,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1187,7 +1198,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1203,7 +1214,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1215,7 +1226,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1223,7 +1234,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1231,7 +1242,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1239,7 +1250,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>源题号</t>
   </si>
@@ -71,6 +71,21 @@
   </si>
   <si>
     <t>P14361</t>
+  </si>
+  <si>
+    <t>U709285</t>
+  </si>
+  <si>
+    <t>U709280</t>
+  </si>
+  <si>
+    <t>U709289</t>
+  </si>
+  <si>
+    <t>U709295</t>
+  </si>
+  <si>
+    <t>U709578</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1053,8 +1068,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1158,6 +1173,46 @@
       </c>
       <c r="B13">
         <v>563</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>608</v>
       </c>
     </row>
   </sheetData>
@@ -1170,7 +1225,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1182,7 +1237,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1190,7 +1245,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1198,7 +1253,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1214,7 +1269,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1226,7 +1281,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1234,7 +1289,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1242,7 +1297,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1250,7 +1305,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>源题号</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>U709578</t>
+  </si>
+  <si>
+    <t>U709780</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1068,8 +1071,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1213,6 +1216,14 @@
       </c>
       <c r="B18">
         <v>608</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -1225,7 +1236,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1237,7 +1248,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1245,7 +1256,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1253,7 +1264,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1269,7 +1280,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1281,7 +1292,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1289,7 +1300,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1297,7 +1308,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1305,7 +1316,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17800"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>源题号</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>U709780</t>
+  </si>
+  <si>
+    <t>U709995</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1071,8 +1074,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1224,6 +1227,14 @@
       </c>
       <c r="B19">
         <v>609</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -1236,7 +1247,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1248,7 +1259,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1256,7 +1267,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1264,7 +1275,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1280,7 +1291,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1292,7 +1303,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1300,7 +1311,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1308,7 +1319,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1316,7 +1327,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>源题号</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>U709995</t>
+  </si>
+  <si>
+    <t>U710009</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1074,7 +1077,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1235,6 +1238,14 @@
       </c>
       <c r="B20">
         <v>610</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -1259,7 +1270,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1267,7 +1278,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1275,7 +1286,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1303,7 +1314,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1311,7 +1322,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1319,7 +1330,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1327,7 +1338,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>源题号</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>U710009</t>
+  </si>
+  <si>
+    <t>U710413</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1077,7 +1080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1246,6 +1249,14 @@
       </c>
       <c r="B21">
         <v>611</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22">
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -1270,7 +1281,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1278,7 +1289,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1286,7 +1297,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1314,7 +1325,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1322,7 +1333,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1330,7 +1341,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1338,7 +1349,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\oi_repo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17800"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>源题号</t>
   </si>
@@ -107,6 +112,9 @@
   </si>
   <si>
     <t>cf26b</t>
+  </si>
+  <si>
+    <t>cf1622a</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1081,7 +1089,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1268,8 +1276,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1301,6 +1309,14 @@
       </c>
       <c r="B4">
         <v>607</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -1313,7 +1329,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1325,7 +1341,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1333,7 +1349,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1341,7 +1357,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1349,7 +1365,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\oi_repo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\oj-resetta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>源题号</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>cf1622a</t>
+  </si>
+  <si>
+    <t>cf1729b</t>
+  </si>
+  <si>
+    <t>cf1979a</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1276,8 +1282,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1317,6 +1323,22 @@
       </c>
       <c r="B5">
         <v>620</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7">
+        <v>625</v>
       </c>
     </row>
   </sheetData>
@@ -1341,7 +1363,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1349,7 +1371,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1357,7 +1379,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1365,7 +1387,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>源题号</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>cf1979a</t>
+  </si>
+  <si>
+    <t>cf1600j</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1282,8 +1285,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="1"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1339,6 +1342,14 @@
       </c>
       <c r="B7">
         <v>625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8">
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -1363,7 +1374,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1371,7 +1382,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1379,7 +1390,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1387,7 +1398,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>源题号</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t>cf1600j</t>
+  </si>
+  <si>
+    <t>cf255a</t>
   </si>
   <si>
     <t>abc036a</t>
@@ -1285,8 +1288,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="1"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1350,6 +1353,14 @@
       </c>
       <c r="B8">
         <v>629</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9">
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -1374,7 +1385,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1382,7 +1393,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1390,7 +1401,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1398,7 +1409,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5">
         <v>600</v>

--- a/mappings.xlsx
+++ b/mappings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="洛谷" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>源题号</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>U710413</t>
+  </si>
+  <si>
+    <t>B3686</t>
   </si>
   <si>
     <t>cf1668b</t>
@@ -1100,7 +1103,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1277,6 +1280,14 @@
       </c>
       <c r="B22">
         <v>612</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23">
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1312,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2">
         <v>592</v>
@@ -1309,7 +1320,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>604</v>
@@ -1317,7 +1328,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4">
         <v>607</v>
@@ -1325,7 +1336,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>620</v>
@@ -1333,7 +1344,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6">
         <v>624</v>
@@ -1341,7 +1352,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7">
         <v>625</v>
@@ -1349,7 +1360,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8">
         <v>629</v>
@@ -1357,7 +1368,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9">
         <v>630</v>
@@ -1385,7 +1396,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>590</v>
@@ -1393,7 +1404,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3">
         <v>589</v>
@@ -1401,7 +1412,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4">
         <v>593</v>
@@ -1409,7 +1420,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>600</v>
